--- a/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda</t>
+          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,16; 20,12</t>
+          <t>17,09; 20,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 21,13</t>
+          <t>17,89; 20,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 19,99</t>
+          <t>17,68; 20,03</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,3; 20,72</t>
+          <t>17,36; 20,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 18,01</t>
+          <t>15,03; 17,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 19,17</t>
+          <t>16,74; 18,99</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,79; 23,54</t>
+          <t>19,76; 23,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,51; 27,89</t>
+          <t>21,89; 27,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,74; 23,93</t>
+          <t>20,76; 24,06</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,36; 21,82</t>
+          <t>19,34; 21,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,88; 23,42</t>
+          <t>18,86; 23,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,6; 22,57</t>
+          <t>19,61; 22,68</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,61; 24,86</t>
+          <t>20,66; 24,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,3; 26,13</t>
+          <t>22,13; 26,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,51; 25,1</t>
+          <t>22,33; 25,15</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,53; 20,18</t>
+          <t>16,62; 20,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,1; 27,96</t>
+          <t>25,24; 28,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,68; 26,1</t>
+          <t>23,78; 26,09</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,6; 20,99</t>
+          <t>19,68; 21,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,98; 22,08</t>
+          <t>20,98; 22,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>18,57</t>
+          <t>18,08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,33</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>18,42</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,09; 20,31</t>
+          <t>16,4; 19,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 20,98</t>
+          <t>17,29; 20,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,68; 20,03</t>
+          <t>17,25; 19,47</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,07</t>
+          <t>18,95</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16,46</t>
+          <t>16,16</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,93</t>
+          <t>17,7</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 20,87</t>
+          <t>17,34; 20,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,03; 17,8</t>
+          <t>14,9; 17,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 18,99</t>
+          <t>16,63; 18,86</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21,54</t>
+          <t>20,62</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24,78</t>
+          <t>23,84</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22,37</t>
+          <t>21,46</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,76; 23,55</t>
+          <t>18,96; 22,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,89; 27,84</t>
+          <t>20,97; 26,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,76; 24,06</t>
+          <t>19,86; 23,02</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>20,51</t>
+          <t>19,95</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>18,75</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20,81</t>
+          <t>19,43</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 21,83</t>
+          <t>18,69; 21,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,86; 23,62</t>
+          <t>17,73; 19,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 22,68</t>
+          <t>18,54; 20,19</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22,69</t>
+          <t>20,94</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24,64</t>
+          <t>24,19</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,91</t>
+          <t>22,87</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,66; 24,65</t>
+          <t>19,0; 22,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,13; 26,07</t>
+          <t>22,98; 25,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,33; 25,15</t>
+          <t>21,71; 24,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>18,43</t>
+          <t>17,06</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26,61</t>
+          <t>25,97</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,92</t>
+          <t>24,24</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,62; 20,21</t>
+          <t>14,7; 19,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,24; 28,0</t>
+          <t>24,48; 27,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,78; 26,09</t>
+          <t>22,95; 25,29</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>20,31</t>
+          <t>19,58</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22,49</t>
+          <t>21,67</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21,48</t>
+          <t>20,64</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,68; 21,03</t>
+          <t>18,84; 20,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,78; 23,29</t>
+          <t>21,09; 22,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,98; 22,12</t>
+          <t>20,19; 21,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q04C1_2023-Clase-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
+          <t>Tiempo medio en años que lleva residiendo en su vivienda (tasa de respuesta: 97,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
